--- a/outputs/per-fund/vc-investments-gnosis-vc.xlsx
+++ b/outputs/per-fund/vc-investments-gnosis-vc.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only GnosisVC. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only GnosisVC. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -6048,11 +6048,11 @@
         <v>1</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>borderless-capital, gnosis-vc</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -6111,11 +6111,11 @@
         <v>1</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures, gnosis-vc</t>
+          <t>electric-capital, framework-ventures, gnosis-vc, parafi-capital</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -6174,11 +6174,11 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>alliance-dao, gnosis-vc, longhash-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -6237,11 +6237,11 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, gnosis-vc</t>
+          <t>1kx, coinbase-ventures, gnosis-vc, longhash-ventures</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -6300,11 +6300,11 @@
         <v>3</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, gnosis-vc</t>
+          <t>alliance-dao, arrington-capital, delphi-ventures, gnosis-vc</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -6359,11 +6359,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, gnosis-vc</t>
+          <t>a16z-crypto, coinbase-ventures, gnosis-vc, polygon-ventures</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -6422,11 +6422,11 @@
         <v>1</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, gnosis-vc, polychain, robot-ventures</t>
+          <t>1kx, amber-group, circle-ventures, figment-capital, gnosis-vc, hack-vc, hypersphere, polychain, polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -6485,11 +6485,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, gnosis-vc</t>
+          <t>alliance-dao, arrington-capital, delphi-ventures, gnosis-vc, hypersphere, sevenx-ventures</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -6544,11 +6544,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, gnosis-vc</t>
+          <t>1kx, circle-ventures, coinbase-ventures, foresight-ventures, gnosis-vc, polygon-ventures</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -6670,11 +6670,11 @@
         <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>gnosis-vc, okx-ventures</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -6851,11 +6851,11 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>gnosis-vc, okx-ventures</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -7038,11 +7038,11 @@
         <v>2</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>arrington-capital, borderless-capital, circle-ventures, gnosis-vc, iosg-ventures, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -7278,11 +7278,11 @@
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>circle-ventures, gnosis-vc</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -7341,11 +7341,11 @@
         <v>1</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>1kx, gnosis-vc</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -7589,11 +7589,11 @@
         <v>1</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>animoca-brands, digital-currency-group, fenbushi-capital, gnosis-vc, gsr</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -7831,11 +7831,11 @@
         <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>gnosis-vc</t>
+          <t>alliance-dao, gnosis-vc</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -9830,19 +9830,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
